--- a/results_exp0/data/optimal/optimal_metrics_train_n8_p60_c10_f1000_s1.xlsx
+++ b/results_exp0/data/optimal/optimal_metrics_train_n8_p60_c10_f1000_s1.xlsx
@@ -531,16 +531,16 @@
         <v>54066493</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00836778912077926</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3475657233817445</v>
+        <v>0.2499445956224121</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3475657233817445</v>
+        <v>0.2499445956224121</v>
       </c>
       <c r="G2" t="n">
-        <v>1511</v>
+        <v>1783</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -555,25 +555,25 @@
         <v>42003081.63764387</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003797460836851289</v>
+        <v>0.003118096336851026</v>
       </c>
       <c r="M2" t="n">
         <v>-22.312</v>
       </c>
       <c r="N2" t="n">
-        <v>54118981</v>
+        <v>54101688.84731774</v>
       </c>
       <c r="O2" t="n">
-        <v>53977540.87148001</v>
+        <v>53976054.97351798</v>
       </c>
       <c r="P2" t="n">
-        <v>0.09356296011818785</v>
+        <v>0.1213834937471494</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.165</v>
+        <v>-0.167</v>
       </c>
       <c r="R2" t="n">
-        <v>3.077898502349854</v>
+        <v>3.592223167419434</v>
       </c>
     </row>
     <row r="3">
@@ -587,16 +587,16 @@
         <v>53798384</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00619833152542814</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5209414149628548</v>
+        <v>0.2150419607873255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5209414149628548</v>
+        <v>0.2150419607873255</v>
       </c>
       <c r="G3" t="n">
-        <v>2468</v>
+        <v>955</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -611,25 +611,25 @@
         <v>42256274.24016403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003817511254617901</v>
+        <v>0.003142931254617771</v>
       </c>
       <c r="M3" t="n">
         <v>-21.454</v>
       </c>
       <c r="N3" t="n">
-        <v>53811824</v>
+        <v>53845571</v>
       </c>
       <c r="O3" t="n">
-        <v>53700750.6706508</v>
+        <v>53699881.36196859</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08401600322583484</v>
+        <v>0.1144798559736744</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.181</v>
+        <v>-0.183</v>
       </c>
       <c r="R3" t="n">
-        <v>3.042443037033081</v>
+        <v>3.581185340881348</v>
       </c>
     </row>
     <row r="4">
@@ -643,16 +643,16 @@
         <v>55986480</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.007950397199957073</v>
       </c>
       <c r="E4" t="n">
-        <v>1.355949953847797</v>
+        <v>0.4314847003728128</v>
       </c>
       <c r="F4" t="n">
-        <v>1.355949953847797</v>
+        <v>0.4314847003728128</v>
       </c>
       <c r="G4" t="n">
-        <v>7355</v>
+        <v>4506</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -667,25 +667,25 @@
         <v>43894904.32210912</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003825170119533306</v>
+        <v>0.003150993119533153</v>
       </c>
       <c r="M4" t="n">
         <v>-21.597</v>
       </c>
       <c r="N4" t="n">
-        <v>56234970</v>
+        <v>56145219.90409644</v>
       </c>
       <c r="O4" t="n">
-        <v>55835194.02733912</v>
+        <v>55828703.0363543</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07883584044752891</v>
+        <v>0.1127817715104823</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.27</v>
+        <v>-0.282</v>
       </c>
       <c r="R4" t="n">
-        <v>3.172218799591064</v>
+        <v>3.57218599319458</v>
       </c>
     </row>
     <row r="5">
@@ -699,16 +699,16 @@
         <v>54308372</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006393721422165341</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.369521819920431</v>
+        <v>0.2468342471046732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.369521819920431</v>
+        <v>0.2468342471046732</v>
       </c>
       <c r="G5" t="n">
-        <v>1755</v>
+        <v>1308</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -723,25 +723,25 @@
         <v>42362320.91907451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003802234170146307</v>
+        <v>0.003127451370146155</v>
       </c>
       <c r="M5" t="n">
         <v>-21.997</v>
       </c>
       <c r="N5" t="n">
-        <v>54406931</v>
+        <v>54394478</v>
       </c>
       <c r="O5" t="n">
-        <v>54212974.01607631</v>
+        <v>54212802.2528403</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07818199662401025</v>
+        <v>0.1185261762914607</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.176</v>
       </c>
       <c r="R5" t="n">
-        <v>3.099698543548584</v>
+        <v>3.612781047821045</v>
       </c>
     </row>
     <row r="6">
@@ -755,16 +755,16 @@
         <v>55168587</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009592985407396028</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7831575292858273</v>
+        <v>0.8238621271996834</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7831575292858273</v>
+        <v>0.8238621271996834</v>
       </c>
       <c r="G6" t="n">
-        <v>1963</v>
+        <v>10398</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -779,25 +779,25 @@
         <v>43254600.73357496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003824247310397251</v>
+        <v>0.003145623810396999</v>
       </c>
       <c r="M6" t="n">
         <v>-21.596</v>
       </c>
       <c r="N6" t="n">
-        <v>55285377</v>
+        <v>55211293.59433962</v>
       </c>
       <c r="O6" t="n">
-        <v>55041670.57856398</v>
+        <v>55037141.59460912</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07888338984991883</v>
+        <v>0.1178936205176003</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.23</v>
+        <v>-0.238</v>
       </c>
       <c r="R6" t="n">
-        <v>3.169386625289917</v>
+        <v>3.689826726913452</v>
       </c>
     </row>
     <row r="7">
@@ -805,22 +805,22 @@
         <v>116</v>
       </c>
       <c r="B7" t="n">
-        <v>57796860</v>
+        <v>57796474</v>
       </c>
       <c r="C7" t="n">
-        <v>57796860</v>
+        <v>57796474</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009927033201035841</v>
+        <v>0.001684675202136943</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7218012108128506</v>
+        <v>0.8512874500021147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7218012108128506</v>
+        <v>0.8512874500021147</v>
       </c>
       <c r="G7" t="n">
-        <v>2112</v>
+        <v>12099</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -835,25 +835,25 @@
         <v>45740956.29582641</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003743138225269422</v>
+        <v>0.00306902102526929</v>
       </c>
       <c r="M7" t="n">
         <v>-20.859</v>
       </c>
       <c r="N7" t="n">
-        <v>57818681</v>
+        <v>57812665</v>
       </c>
       <c r="O7" t="n">
-        <v>57682495.77999271</v>
+        <v>57673350.15983523</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09997763219610019</v>
+        <v>0.1213906703779866</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.198</v>
+        <v>-0.213</v>
       </c>
       <c r="R7" t="n">
-        <v>3.005888700485229</v>
+        <v>3.638913154602051</v>
       </c>
     </row>
     <row r="8">
@@ -867,16 +867,16 @@
         <v>52608511</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00940786144607321</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.317244314366018</v>
+        <v>0.8233905920442361</v>
       </c>
       <c r="F8" t="n">
-        <v>1.317244314366018</v>
+        <v>0.8233905920442361</v>
       </c>
       <c r="G8" t="n">
-        <v>3254</v>
+        <v>12467</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -891,25 +891,25 @@
         <v>40013477.62121775</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00367502918726275</v>
+        <v>0.003000056587262601</v>
       </c>
       <c r="M8" t="n">
         <v>-23.941</v>
       </c>
       <c r="N8" t="n">
-        <v>52724240.97709979</v>
+        <v>52683410</v>
       </c>
       <c r="O8" t="n">
-        <v>52463377.16582838</v>
+        <v>52462932.51565191</v>
       </c>
       <c r="P8" t="n">
-        <v>0.07812291256686589</v>
+        <v>0.1159394385975363</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.276</v>
+        <v>-0.277</v>
       </c>
       <c r="R8" t="n">
-        <v>2.990378856658936</v>
+        <v>3.616533756256104</v>
       </c>
     </row>
     <row r="9">
@@ -923,16 +923,16 @@
         <v>53026531</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0006236825022255451</v>
+        <v>0.008502735553931955</v>
       </c>
       <c r="E9" t="n">
-        <v>1.205924642810801</v>
+        <v>0.8411358658067887</v>
       </c>
       <c r="F9" t="n">
-        <v>1.205924642810801</v>
+        <v>0.8411358658067887</v>
       </c>
       <c r="G9" t="n">
-        <v>5959</v>
+        <v>5599</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -947,25 +947,25 @@
         <v>40546560.83640151</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004309823905544799</v>
+        <v>0.003332072505544636</v>
       </c>
       <c r="M9" t="n">
         <v>-23.535</v>
       </c>
       <c r="N9" t="n">
-        <v>53079491</v>
+        <v>53062158</v>
       </c>
       <c r="O9" t="n">
-        <v>52925171.80022707</v>
+        <v>52902959.78551167</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1008195922547128</v>
+        <v>0.1339712198628397</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.191</v>
+        <v>-0.233</v>
       </c>
       <c r="R9" t="n">
-        <v>3.098801136016846</v>
+        <v>3.716837406158447</v>
       </c>
     </row>
     <row r="10">
@@ -979,16 +979,16 @@
         <v>55002537</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006536243407252185</v>
+        <v>0.009355916764365724</v>
       </c>
       <c r="E10" t="n">
-        <v>1.681114346104781</v>
+        <v>1.204943689189838</v>
       </c>
       <c r="F10" t="n">
-        <v>1.681114346104781</v>
+        <v>1.204943689189838</v>
       </c>
       <c r="G10" t="n">
-        <v>7971</v>
+        <v>4886</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1003,25 +1003,25 @@
         <v>43084198.69628191</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003906598397466543</v>
+        <v>0.003233595297466389</v>
       </c>
       <c r="M10" t="n">
         <v>-21.669</v>
       </c>
       <c r="N10" t="n">
-        <v>55070110</v>
+        <v>55194618</v>
       </c>
       <c r="O10" t="n">
-        <v>54834798.95555715</v>
+        <v>54792929.99334013</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1173371810696657</v>
+        <v>0.1177594283862153</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.305</v>
+        <v>-0.381</v>
       </c>
       <c r="R10" t="n">
-        <v>3.049897432327271</v>
+        <v>3.640697240829468</v>
       </c>
     </row>
     <row r="11">
@@ -1029,22 +1029,22 @@
         <v>197</v>
       </c>
       <c r="B11" t="n">
-        <v>55669066</v>
+        <v>55668964</v>
       </c>
       <c r="C11" t="n">
-        <v>55669066</v>
+        <v>55668964</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003277555424996917</v>
+        <v>0.007984066029117292</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6617649143040796</v>
+        <v>0.876426721922378</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6617649143040796</v>
+        <v>0.876426721922378</v>
       </c>
       <c r="G11" t="n">
-        <v>1647</v>
+        <v>3299</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>44042787.55811303</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003827211997455708</v>
+        <v>0.003152828297455551</v>
       </c>
       <c r="M11" t="n">
-        <v>-20.885</v>
+        <v>-20.884</v>
       </c>
       <c r="N11" t="n">
-        <v>55869160.61242786</v>
+        <v>55761831</v>
       </c>
       <c r="O11" t="n">
-        <v>55509896.86141277</v>
+        <v>55506734.94507111</v>
       </c>
       <c r="P11" t="n">
-        <v>0.07707260067381948</v>
+        <v>0.116082765119195</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.286</v>
+        <v>-0.291</v>
       </c>
       <c r="R11" t="n">
-        <v>3.041455507278442</v>
+        <v>3.634174585342407</v>
       </c>
     </row>
     <row r="12">
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.074790524523335</v>
+        <v>0.5146749326755409</v>
       </c>
       <c r="F12" t="n">
-        <v>1.074790524523335</v>
+        <v>0.5146749326755409</v>
       </c>
       <c r="G12" t="n">
-        <v>5420</v>
+        <v>5422</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1115,25 +1115,25 @@
         <v>44213893.82828662</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003804671924726009</v>
+        <v>0.003129809824725865</v>
       </c>
       <c r="M12" t="n">
         <v>-21.665</v>
       </c>
       <c r="N12" t="n">
-        <v>56645497.57664555</v>
+        <v>56494831</v>
       </c>
       <c r="O12" t="n">
-        <v>56280791.72534288</v>
+        <v>56282796.13349639</v>
       </c>
       <c r="P12" t="n">
-        <v>0.09462373370989331</v>
+        <v>0.1199102479696809</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.286</v>
+        <v>-0.283</v>
       </c>
       <c r="R12" t="n">
-        <v>3.016282081604004</v>
+        <v>3.643935203552246</v>
       </c>
     </row>
     <row r="13">
@@ -1147,16 +1147,16 @@
         <v>55927721</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005783184909298267</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0216754648799</v>
+        <v>0.4811118709541578</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0216754648799</v>
+        <v>0.4811118709541578</v>
       </c>
       <c r="G13" t="n">
-        <v>5177</v>
+        <v>5128</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1171,25 +1171,25 @@
         <v>44156519.206066</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003854976802127812</v>
+        <v>0.00318082840212767</v>
       </c>
       <c r="M13" t="n">
         <v>-21.047</v>
       </c>
       <c r="N13" t="n">
-        <v>56002599</v>
+        <v>55983999</v>
       </c>
       <c r="O13" t="n">
-        <v>55819775.20397173</v>
+        <v>55820973.18403027</v>
       </c>
       <c r="P13" t="n">
-        <v>0.08086302879480742</v>
+        <v>0.1201479177918158</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.193</v>
+        <v>-0.191</v>
       </c>
       <c r="R13" t="n">
-        <v>2.973325252532959</v>
+        <v>3.612589836120605</v>
       </c>
     </row>
   </sheetData>
